--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">25-180</t>
   </si>
   <si>
-    <t xml:space="preserve">Dynamic Physical Therapy</t>
+    <t xml:space="preserve">Dynamic PT</t>
   </si>
   <si>
     <t xml:space="preserve">CALA</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Mirabelli</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">CA9</t>
   </si>
   <si>
     <t xml:space="preserve">Grant</t>
@@ -126,6 +126,9 @@
     <t xml:space="preserve">R.W.</t>
   </si>
   <si>
+    <t xml:space="preserve">DCCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">(7-2)</t>
   </si>
   <si>
@@ -135,6 +138,9 @@
     <t xml:space="preserve">Zorn</t>
   </si>
   <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
     <t xml:space="preserve">(6-3)</t>
   </si>
   <si>
@@ -231,9 +237,6 @@
     <t xml:space="preserve">Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jackson</t>
   </si>
   <si>
@@ -276,9 +279,6 @@
     <t xml:space="preserve">Rico</t>
   </si>
   <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
     <t xml:space="preserve">24-924</t>
   </si>
   <si>
@@ -297,13 +297,13 @@
     <t xml:space="preserve">24-724</t>
   </si>
   <si>
-    <t xml:space="preserve">Hain Celestial Group</t>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
   </si>
   <si>
     <t xml:space="preserve">24-1287</t>
   </si>
   <si>
-    <t xml:space="preserve">Learning Resource</t>
+    <t xml:space="preserve">Learning Resources</t>
   </si>
   <si>
     <t xml:space="preserve">CAFED</t>
@@ -1135,7 +1135,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -1160,13 +1160,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1258,27 +1258,27 @@
         <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1293,27 +1293,27 @@
         <v>197</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1334,21 +1334,21 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1363,27 +1363,27 @@
         <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1398,27 +1398,27 @@
         <v>140</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1436,24 +1436,24 @@
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1474,21 +1474,21 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1509,21 +1509,21 @@
         <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1538,27 +1538,27 @@
         <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1630,16 +1630,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
         <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
         <v>86</v>
@@ -1689,18 +1689,18 @@
         <v>171</v>
       </c>
       <c r="I3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
         <v>88</v>
@@ -1724,18 +1724,18 @@
         <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>91</v>
@@ -1744,7 +1744,7 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1759,18 +1759,18 @@
         <v>113</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>93</v>
@@ -1794,18 +1794,18 @@
         <v>108</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>96</v>
@@ -1814,7 +1814,7 @@
         <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>98</v>
@@ -1837,7 +1837,7 @@
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1852,18 +1852,18 @@
         <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
         <v>100</v>
@@ -1872,7 +1872,7 @@
         <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>102</v>
@@ -1895,7 +1895,7 @@
         <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -2014,13 +2014,13 @@
         <v>94</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -2034,7 +2034,7 @@
         <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -2069,7 +2069,7 @@
         <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2084,13 +2084,13 @@
         <v>108</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -2150,16 +2150,20 @@
         <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="n">
+        <v>46001</v>
+      </c>
       <c r="G8" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="H8"/>
+      <c r="H8" t="n">
+        <v>163</v>
+      </c>
       <c r="I8" t="s">
         <v>121</v>
       </c>
@@ -2181,7 +2185,7 @@
         <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2250,7 +2254,7 @@
         <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2265,13 +2269,13 @@
         <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
         <v>127</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -2285,7 +2289,7 @@
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2346,13 +2350,13 @@
         <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -2366,7 +2370,7 @@
         <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2404,13 +2408,13 @@
         <v>122</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -2493,7 +2497,7 @@
         <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2508,13 +2512,13 @@
         <v>88</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -2566,13 +2570,13 @@
         <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -2609,7 +2613,7 @@
         <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2632,7 +2636,7 @@
         <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2655,7 +2659,7 @@
         <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2676,7 +2680,7 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2740,7 @@
         <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2782,7 +2786,7 @@
         <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2797,13 +2801,13 @@
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -2817,7 +2821,7 @@
         <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2840,7 +2844,7 @@
         <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2863,7 +2867,7 @@
         <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2886,7 +2890,7 @@
         <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2909,7 +2913,7 @@
         <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2978,7 +2982,7 @@
         <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3024,7 +3028,7 @@
         <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3047,7 +3051,7 @@
         <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3116,7 +3120,7 @@
         <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3139,7 +3143,7 @@
         <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -108,177 +108,183 @@
     <t xml:space="preserve">(8-1)</t>
   </si>
   <si>
-    <t xml:space="preserve">25A810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mirabelli</t>
+    <t xml:space="preserve">25-248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellingburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-5438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacate and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-5774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCATX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico</t>
   </si>
   <si>
     <t xml:space="preserve">CA9</t>
   </si>
   <si>
-    <t xml:space="preserve">Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R.W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elingburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-5438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacate and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-5774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarreal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCATX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico</t>
-  </si>
-  <si>
     <t xml:space="preserve">24-924</t>
   </si>
   <si>
@@ -558,7 +564,7 @@
     <t xml:space="preserve">25-406</t>
   </si>
   <si>
-    <t xml:space="preserve">AT&amp;T</t>
+    <t xml:space="preserve">AT\&amp;T</t>
   </si>
   <si>
     <t xml:space="preserve">25-429</t>
@@ -1111,14 +1117,14 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="n">
-        <v>46083</v>
+        <v>46132</v>
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -1142,11 +1148,11 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="n">
-        <v>46132</v>
+        <v>46104</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -1166,23 +1172,54 @@
         <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="n">
-        <v>46104</v>
+        <v>46168</v>
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="K8" t="s">
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1234,16 +1271,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1258,27 +1295,27 @@
         <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1293,27 +1330,27 @@
         <v>197</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1334,21 +1371,21 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
         <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>58</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1363,27 +1400,27 @@
         <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1398,27 +1435,27 @@
         <v>140</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1436,24 +1473,24 @@
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1474,21 +1511,21 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1509,21 +1546,21 @@
         <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1538,27 +1575,27 @@
         <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1579,7 +1616,7 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1630,16 +1667,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1660,18 +1697,18 @@
         <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -1689,27 +1726,27 @@
         <v>171</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1724,27 +1761,27 @@
         <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1759,27 +1796,27 @@
         <v>113</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1794,27 +1831,27 @@
         <v>108</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1828,16 +1865,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1852,60 +1889,84 @@
         <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H9" t="n">
+        <v>198</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
+      <c r="F10" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H10" t="n">
+        <v>198</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1955,13 +2016,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1985,21 +2046,21 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2014,27 +2075,27 @@
         <v>94</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2055,21 +2116,21 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2084,27 +2145,27 @@
         <v>108</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2118,16 +2179,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2141,16 +2202,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2165,10 +2226,10 @@
         <v>163</v>
       </c>
       <c r="I8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -2176,16 +2237,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2245,16 +2306,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2269,27 +2330,27 @@
         <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2303,13 +2364,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -2326,16 +2387,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2350,27 +2411,27 @@
         <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2384,16 +2445,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2408,27 +2469,27 @@
         <v>122</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -2488,16 +2549,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2512,27 +2573,27 @@
         <v>88</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2546,16 +2607,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2570,27 +2631,27 @@
         <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2604,16 +2665,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2627,16 +2688,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2650,16 +2711,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2680,7 +2741,7 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2731,39 +2792,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
+      <c r="F2" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2777,16 +2850,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2801,73 +2874,97 @@
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
+      <c r="F5" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="H5" t="n">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H6" t="n">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2881,39 +2978,51 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="F8" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="H8" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2973,36 +3082,48 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
+      <c r="F2" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -3019,39 +3140,51 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
+      <c r="F4" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3065,13 +3198,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -3088,16 +3221,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3111,16 +3244,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3134,16 +3267,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3157,26 +3290,38 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
+      <c r="F10" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -2251,12 +2251,24 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="H9" t="n">
+        <v>184</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -6,20 +6,20 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="No_Argument" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="October" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="November" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="December" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="January" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="February" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="March" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="April" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="April" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="December" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="February" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="January" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="March" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="November" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="October" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="No_Argument" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -54,9 +54,534 @@
     <t xml:space="preserve">author</t>
   </si>
   <si>
+    <t xml:space="preserve">April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacate and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsanto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMOE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-1083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin v. Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sripetch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMD Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FS Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urias-Orellana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">February</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enbridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exxon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquemines Parish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Little</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAM Pension Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25A312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.P.J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wolford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-5146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abouammo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flowers Foods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keathley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Otro Lado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-7351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitchford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coney Island Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hencely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutherford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-5774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-5438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellingburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCATX</t>
+  </si>
+  <si>
     <t xml:space="preserve">No Argument</t>
   </si>
   <si>
+    <t xml:space="preserve">25-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margolin</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-1159</t>
   </si>
   <si>
@@ -66,58 +591,13 @@
     <t xml:space="preserve">SCMS</t>
   </si>
   <si>
-    <t xml:space="preserve">Reverse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R.W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
+    <t xml:space="preserve">25-580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GVR</t>
   </si>
   <si>
     <t xml:space="preserve">25-297</t>
@@ -126,484 +606,10 @@
     <t xml:space="preserve">Zorn</t>
   </si>
   <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margolin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whitton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ellingburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-5438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacate and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-5774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarreal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCATX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hencely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coney Island Auto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hain Celestial Grp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rutherford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urias-Orellana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slaughter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRSC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FS Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">January</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaquemines Parish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Little</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.P.J.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wolford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAM Pension Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25A312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">February</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Havana Docks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exxon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enbridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montgomery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-7351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitchford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-5146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abouammo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flowers Foods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al Otro Lado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keathley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sripetch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UMD Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT\&amp;T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsanto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-1083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mullin v. DOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hikma</t>
+    <t xml:space="preserve">25-748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McCarthy</t>
   </si>
 </sst>
 </file>
@@ -991,11 +997,15 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="n">
+        <v>46134</v>
+      </c>
       <c r="G2" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="H2"/>
+        <v>46196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>63</v>
+      </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -1023,49 +1033,45 @@
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1" t="n">
-        <v>45985</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3"/>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="H4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I4" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="H4"/>
-      <c r="I4" t="s">
-        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1079,24 +1085,28 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="1" t="n">
+        <v>46133</v>
+      </c>
       <c r="G5" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="H5"/>
+        <v>46177</v>
+      </c>
+      <c r="H5" t="n">
+        <v>45</v>
+      </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1104,30 +1114,34 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="G6" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="H6"/>
+        <v>46177</v>
+      </c>
+      <c r="H6" t="n">
+        <v>37</v>
+      </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1135,30 +1149,34 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="G7" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="H7"/>
+        <v>46198</v>
+      </c>
+      <c r="H7" t="n">
+        <v>60</v>
+      </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -1166,30 +1184,34 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="n">
+        <v>46141</v>
+      </c>
       <c r="G8" s="1" t="n">
-        <v>46168</v>
-      </c>
-      <c r="H8"/>
+        <v>46198</v>
+      </c>
+      <c r="H8" t="n">
+        <v>58</v>
+      </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1197,30 +1219,69 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="G9" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="H9"/>
+        <v>46177</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46</v>
+      </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1271,352 +1332,258 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45945</v>
+        <v>45992</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46036</v>
+        <v>46106</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45945</v>
+        <v>45993</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46141</v>
       </c>
       <c r="H3" t="n">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45944</v>
+        <v>46001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46042</v>
+        <v>46184</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45944</v>
+        <v>46001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46031</v>
+        <v>46163</v>
       </c>
       <c r="H5" t="n">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="I5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>45938</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>46077</v>
-      </c>
-      <c r="H6" t="n">
-        <v>140</v>
-      </c>
-      <c r="I6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" t="s">
-        <v>66</v>
-      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45938</v>
+        <v>45994</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46036</v>
+        <v>46101</v>
       </c>
       <c r="H7" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>46036</v>
-      </c>
-      <c r="H8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" t="s">
-        <v>73</v>
-      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45937</v>
+        <v>45992</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46112</v>
+        <v>46085</v>
       </c>
       <c r="H9" t="n">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>46078</v>
-      </c>
-      <c r="H10" t="n">
-        <v>143</v>
-      </c>
-      <c r="I10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="H11" t="n">
-        <v>107</v>
-      </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1667,305 +1634,247 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45964</v>
+        <v>46079</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="H2" t="n">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45964</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46134</v>
+        <v>46196</v>
       </c>
       <c r="H3" t="n">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45965</v>
+        <v>46076</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46042</v>
+        <v>46163</v>
       </c>
       <c r="H4" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45965</v>
+        <v>46084</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46077</v>
+        <v>46191</v>
       </c>
       <c r="H5" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45966</v>
+        <v>46085</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46073</v>
+        <v>46156</v>
       </c>
       <c r="H6" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="F7" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="H7" t="n">
+        <v>119</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45971</v>
+        <v>46083</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46078</v>
+        <v>46191</v>
       </c>
       <c r="H8" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="H9" t="n">
-        <v>198</v>
-      </c>
-      <c r="I9" t="s">
         <v>47</v>
-      </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="H10" t="n">
-        <v>198</v>
-      </c>
-      <c r="I10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2016,159 +1925,147 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45992</v>
+        <v>46034</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46106</v>
+        <v>46129</v>
       </c>
       <c r="H2" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45992</v>
+        <v>46036</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46085</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>46141</v>
-      </c>
-      <c r="H4" t="n">
-        <v>149</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>77</v>
-      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45994</v>
+        <v>46042</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46101</v>
+        <v>46163</v>
       </c>
       <c r="H5" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2179,16 +2076,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2202,72 +2099,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46001</v>
+        <v>46042</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46163</v>
+        <v>46198</v>
       </c>
       <c r="H8" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I8" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>46001</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="H9" t="n">
-        <v>184</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2318,193 +2180,229 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46034</v>
+        <v>46111</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46129</v>
+        <v>46184</v>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
+      <c r="F4" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46036</v>
+        <v>46105</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46085</v>
+        <v>46184</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="H6" t="n">
+        <v>94</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46042</v>
+        <v>46112</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="H7" t="n">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
         <v>126</v>
       </c>
-      <c r="B8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" t="s">
-        <v>142</v>
-      </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -2512,6 +2410,29 @@
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2561,199 +2482,317 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46076</v>
+        <v>45965</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46163</v>
+        <v>46042</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H3" t="n">
+        <v>198</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46079</v>
+        <v>45971</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="H4" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
+      <c r="F5" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="H5" t="n">
+        <v>113</v>
+      </c>
+      <c r="I5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="H6" t="n">
+        <v>171</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="F7" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="H7" t="n">
+        <v>226</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" t="s">
         <v>143</v>
       </c>
-      <c r="B8" t="s">
-        <v>156</v>
-      </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46085</v>
+        <v>45966</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46156</v>
+        <v>46073</v>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="H9" t="n">
+        <v>143</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="H10" t="n">
+        <v>198</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2804,247 +2843,353 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46112</v>
+        <v>45937</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46170</v>
+        <v>46036</v>
       </c>
       <c r="H2" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>107</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46111</v>
+        <v>45938</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46156</v>
+        <v>46036</v>
       </c>
       <c r="H4" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46111</v>
+        <v>45944</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46184</v>
+        <v>46031</v>
       </c>
       <c r="H5" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" t="s">
         <v>158</v>
       </c>
-      <c r="B6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" t="s">
-        <v>168</v>
-      </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46106</v>
+        <v>45945</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46170</v>
+        <v>46036</v>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="F7" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="H7" t="n">
+        <v>176</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46105</v>
+        <v>45944</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46184</v>
+        <v>46042</v>
       </c>
       <c r="H8" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>167</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="H9" t="n">
+        <v>197</v>
+      </c>
+      <c r="I9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="H10" t="n">
+        <v>140</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="H11" t="n">
+        <v>143</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3094,129 +3239,137 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
         <v>175</v>
       </c>
-      <c r="B2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>46132</v>
-      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46</v>
-      </c>
+        <v>45985</v>
+      </c>
+      <c r="H2"/>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
         <v>178</v>
       </c>
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
         <v>180</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>181</v>
       </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>46133</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H4" t="n">
-        <v>45</v>
-      </c>
+        <v>45999</v>
+      </c>
+      <c r="H4"/>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5" t="s">
         <v>182</v>
       </c>
-      <c r="C5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -3225,114 +3378,142 @@
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="n">
+        <v>46168</v>
+      </c>
       <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="I6" t="s">
+        <v>182</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="n">
+        <v>45985</v>
+      </c>
       <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="n">
+        <v>46174</v>
+      </c>
       <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="I8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="n">
+        <v>46104</v>
+      </c>
       <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>46141</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H10" t="n">
-        <v>37</v>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="H10"/>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -84,6 +84,9 @@
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-856</t>
   </si>
   <si>
@@ -234,9 +237,6 @@
     <t xml:space="preserve">Reverse</t>
   </si>
   <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
     <t xml:space="preserve">25-332</t>
   </si>
   <si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deny</t>
   </si>
   <si>
     <t xml:space="preserve">24-43</t>
@@ -1032,25 +1035,37 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H3" t="n">
+        <v>64</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1065,13 +1080,13 @@
         <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1079,13 +1094,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1100,13 +1115,13 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -1114,13 +1129,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1135,13 +1150,13 @@
         <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -1149,13 +1164,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1170,13 +1185,13 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -1184,10 +1199,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1205,13 +1220,13 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1219,13 +1234,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1240,13 +1255,13 @@
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1254,10 +1269,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
@@ -1275,13 +1290,13 @@
         <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1332,13 +1347,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1356,10 +1371,10 @@
         <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
@@ -1367,16 +1382,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1391,24 +1406,24 @@
         <v>149</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1426,27 +1441,27 @@
         <v>184</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1461,27 +1476,27 @@
         <v>163</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1495,16 +1510,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1519,18 +1534,18 @@
         <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
@@ -1544,16 +1559,28 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="F8" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H8" t="n">
+        <v>204</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
@@ -1577,13 +1604,13 @@
         <v>94</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1643,7 +1670,7 @@
         <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1658,13 +1685,13 @@
         <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -1693,13 +1720,13 @@
         <v>121</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -1713,7 +1740,7 @@
         <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1731,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -1748,7 +1775,7 @@
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1766,10 +1793,10 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -1798,13 +1825,13 @@
         <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1818,7 +1845,7 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1836,10 +1863,10 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -1853,7 +1880,7 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1868,13 +1895,13 @@
         <v>109</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1961,7 @@
         <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1984,13 +2011,13 @@
         <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -2004,7 +2031,7 @@
         <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2042,13 +2069,13 @@
         <v>122</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -2067,22 +2094,34 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -2102,13 +2141,13 @@
         <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2123,13 +2162,13 @@
         <v>157</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2180,16 +2219,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2204,27 +2243,27 @@
         <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2239,24 +2278,24 @@
         <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -2274,27 +2313,27 @@
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2312,24 +2351,24 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2344,27 +2383,27 @@
         <v>94</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2379,24 +2418,24 @@
         <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
         <v>77</v>
@@ -2413,26 +2452,38 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H9" t="n">
+        <v>99</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2482,16 +2533,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2506,24 +2557,24 @@
         <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2541,27 +2592,27 @@
         <v>198</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2576,27 +2627,27 @@
         <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2611,24 +2662,24 @@
         <v>113</v>
       </c>
       <c r="I5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -2657,16 +2708,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2681,24 +2732,24 @@
         <v>226</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
@@ -2722,21 +2773,21 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2751,27 +2802,27 @@
         <v>143</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2786,13 +2837,13 @@
         <v>198</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2843,13 +2894,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -2867,27 +2918,27 @@
         <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2902,24 +2953,24 @@
         <v>107</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
         <v>89</v>
@@ -2937,27 +2988,27 @@
         <v>99</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2975,24 +3026,24 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3007,27 +3058,27 @@
         <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3042,27 +3093,27 @@
         <v>176</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3077,27 +3128,27 @@
         <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3112,27 +3163,27 @@
         <v>197</v>
       </c>
       <c r="I9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3150,7 +3201,7 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -3158,16 +3209,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3182,13 +3233,13 @@
         <v>143</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3239,13 +3290,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -3259,27 +3310,27 @@
       </c>
       <c r="H2"/>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3290,27 +3341,27 @@
       </c>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3321,24 +3372,24 @@
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -3352,24 +3403,24 @@
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -3383,27 +3434,27 @@
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3414,27 +3465,27 @@
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3445,24 +3496,24 @@
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -3476,24 +3527,24 @@
       </c>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -3507,13 +3558,13 @@
       </c>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -324,12 +324,6 @@
     <t xml:space="preserve">SCPA</t>
   </si>
   <si>
-    <t xml:space="preserve">24-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Little</t>
-  </si>
-  <si>
     <t xml:space="preserve">23-1209</t>
   </si>
   <si>
@@ -474,7 +468,7 @@
     <t xml:space="preserve">October</t>
   </si>
   <si>
-    <t xml:space="preserve">24-5774</t>
+    <t xml:space="preserve">25-5774</t>
   </si>
   <si>
     <t xml:space="preserve">24-440</t>
@@ -1501,12 +1495,24 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H6" t="n">
+        <v>204</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -2031,17 +2037,29 @@
         <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
+      <c r="F4" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="H4" t="n">
+        <v>122</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2057,25 +2075,25 @@
         <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46163</v>
+        <v>46202</v>
       </c>
       <c r="H5" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2083,34 +2101,34 @@
         <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46043</v>
+        <v>46035</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="H6" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -2124,50 +2142,27 @@
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H7" t="n">
         <v>157</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I7" t="s">
         <v>25</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2219,13 +2214,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
         <v>112</v>
-      </c>
-      <c r="B2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" t="s">
-        <v>114</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -2254,16 +2249,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" t="s">
         <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>117</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2289,13 +2284,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -2324,13 +2319,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
@@ -2359,13 +2354,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -2394,13 +2389,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -2429,13 +2424,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
         <v>77</v>
@@ -2443,22 +2438,34 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="F8" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H8" t="n">
+        <v>91</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -2533,13 +2540,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" t="s">
         <v>130</v>
-      </c>
-      <c r="B2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" t="s">
-        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>68</v>
@@ -2568,13 +2575,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2603,16 +2610,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2627,7 +2634,7 @@
         <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s">
         <v>35</v>
@@ -2638,13 +2645,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
@@ -2662,7 +2669,7 @@
         <v>113</v>
       </c>
       <c r="I5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s">
         <v>35</v>
@@ -2673,13 +2680,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -2708,13 +2715,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -2743,13 +2750,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
@@ -2778,13 +2785,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -2813,13 +2820,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
@@ -2894,10 +2901,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -2929,13 +2936,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
-        <v>152</v>
-      </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
         <v>58</v>
@@ -2964,13 +2971,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
         <v>89</v>
@@ -2999,13 +3006,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
         <v>63</v>
@@ -3034,16 +3041,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" t="s">
         <v>158</v>
-      </c>
-      <c r="C6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" t="s">
-        <v>160</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3069,16 +3076,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3104,16 +3111,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" t="s">
         <v>163</v>
-      </c>
-      <c r="C8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" t="s">
-        <v>165</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3139,16 +3146,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" t="s">
         <v>166</v>
-      </c>
-      <c r="C9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" t="s">
-        <v>168</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3163,7 +3170,7 @@
         <v>197</v>
       </c>
       <c r="I9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -3174,13 +3181,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -3209,16 +3216,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" t="s">
         <v>171</v>
-      </c>
-      <c r="C11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" t="s">
-        <v>173</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3290,13 +3297,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" t="s">
         <v>174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" t="s">
-        <v>176</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -3321,16 +3328,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" t="s">
         <v>177</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" t="s">
-        <v>179</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3352,16 +3359,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" t="s">
         <v>180</v>
-      </c>
-      <c r="C4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D4" t="s">
-        <v>182</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3372,7 +3379,7 @@
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J4" t="s">
         <v>35</v>
@@ -3383,13 +3390,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -3403,7 +3410,7 @@
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
@@ -3414,13 +3421,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -3434,7 +3441,7 @@
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J6" t="s">
         <v>35</v>
@@ -3445,16 +3452,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
         <v>188</v>
-      </c>
-      <c r="C7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" t="s">
-        <v>190</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3476,13 +3483,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -3496,7 +3503,7 @@
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J8" t="s">
         <v>40</v>
@@ -3507,13 +3514,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -3538,13 +3545,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -3558,7 +3565,7 @@
       </c>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
